--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -413,219 +413,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>字段中文名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>字段所属类型</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>业务含义</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>枚举值</t>
+          <t>基本信息</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>字段中文名</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>字符型</t>
+          <t>字段所属类型</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>记录客户在系统中的注册名称，用于唯一标识客户身份</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>业务含义</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>枚举值</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>客户状态</t>
+          <t>客户名称</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>代码枚举类</t>
+          <t>文本类</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>标识客户在系统中的当前状态，包括正常、冻结、注销等</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>01-正常;02-冻结;03-注销</t>
+          <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>交易金额</t>
+          <t>开户日期</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>数值型</t>
+          <t>日期时间类</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>记录一笔交易的实际发生金额，单位为元</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>开户的日期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>客户类型</t>
+          <t>手机号码</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>代码枚举类</t>
+          <t>文本类</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>客户类型</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>01-个人;02-企业</t>
+          <t>客户手机号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>账户余额</t>
+          <t>客户状态</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>数值型</t>
+          <t>代码枚举类</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>账户的余额</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>标识客户在系统中的当前状态，包括正常、冻结、注销等</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>01-正常;02-冻结;03-注销</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>交易状态</t>
+          <t>交易金额</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>代码枚举类</t>
+          <t>数值类</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>交易的状态</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>01-成功,02-失败,03-处理中</t>
+          <t>记录一笔交易的实际发生金额，单位为元</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>客户姓名</t>
+          <t>第二结论类型</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>字符型</t>
+          <t>代码枚举类</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>客户的名字</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>第二结论类型</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>01-通过;02-拒绝</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDA规则结果</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>字符型</t>
+          <t>代码枚举类</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>记录客户的电子邮箱地址</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>CDA的规则结果</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>01-命中;02-未命中</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>证件类型</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>CDA规则结果</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>代码枚举类</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>标识客户使用的证件类型</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>身份证;护照;军官证</t>
+          <t>CDA规则结果字段</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>手机号码</t>
+          <t>转案欺诈类型</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>字符型</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>代码枚举类</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>指转案欺诈的不同类别</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01-欺诈;02-正常</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>支付方式</t>
+          <t>CDA规则结果</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -635,19 +631,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>记录客户选择的支付方式类型</t>
+          <t>信用风险评估系统CDA引擎生成的规则判定结果，用于自动审批决策</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.现金 2.银行卡 3.支票 4.汇款</t>
+          <t>01-命中;02-未命中</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>性别</t>
+          <t>转案欺诈类型</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -657,60 +653,221 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>标识客户的性别信息</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>男/女</t>
+          <t>标记案件转案过程中涉及的欺诈行为分类，由风控系统自动识别</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>信用等级</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>代码枚举类</t>
+          <t>文本类</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>反映客户的信用评级，由风控系统定期计算更新</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>(A)优秀 (B)良好 (C)一般 (D)较差</t>
+          <t>记录客户的电子邮箱地址</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>证件类型</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>标识客户使用的证件类型</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>身份证;护照;军官证</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>账户余额</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>数值类</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>银行卡号</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>字符型</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>记录客户绑定的银行卡卡号，用于资金划转</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>是否VIP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>布尔型</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>标识客户是否为VIP用户</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>支付方式</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>代码枚举类</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>记录客户选择的支付方式类型</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.现金 2.银行卡 3.支票 4.汇款</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>性别</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>代码枚举类</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>标识客户的性别信息</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>男/女</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>信用等级</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>代码枚举类</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>反映客户的信用评级，由风控系统定期计算更新</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(A)优秀 (B)良好 (C)一般 (D)较差</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>币种代码</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>代码枚举类</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标识交易使用的货币类型代码</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>编码类</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>标识交易使用的货币类型代码，遵循ISO 4217标准</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>01：人民币 02：美元 03：欧元</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>是否冻结</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>标志类</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>标识账户是否被冻结，冻结后无法进行交易操作</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Y-是;N-否</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>交易状态</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>代码枚举类</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>记录交易的当前处理状态</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>01-成功;02-失败;03-处理中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>